--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FA2956-4F5D-4A36-9431-A07BCDCFF76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A324BA9-873B-46D5-A165-0F796190B2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="2190" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4170" yWindow="1395" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listening" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -453,7 +453,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <f t="shared" ref="A5:A11" si="0">A4+1</f>
+        <f t="shared" ref="A5:A64" si="0">A4+1</f>
         <v>4</v>
       </c>
       <c r="B5">
@@ -539,6 +539,384 @@
       </c>
       <c r="C11">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -690,122 +1068,182 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>131</v>
@@ -1023,7 +1461,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <f t="shared" ref="A68:A102" si="1">A67+1</f>
+        <f t="shared" ref="A68:A101" si="1">A67+1</f>
         <v>167</v>
       </c>
     </row>

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A324BA9-873B-46D5-A165-0F796190B2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFEF148-12FD-468D-9DF7-CEE9C1BCEBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4170" yWindow="1395" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -666,59 +666,119 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1188,59 +1248,119 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3">

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFEF148-12FD-468D-9DF7-CEE9C1BCEBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC789CD-A4DE-4F99-B9AD-E23D4E44140F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="1395" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8220" yWindow="120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listening" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -786,98 +786,158 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1368,98 +1428,158 @@
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>147</v>

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC789CD-A4DE-4F99-B9AD-E23D4E44140F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92ED4F3-BCEB-4D68-9074-816630C0D282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8220" yWindow="120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1785" yWindow="1005" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listening" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -906,134 +906,188 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -1548,134 +1602,206 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>163</v>

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92ED4F3-BCEB-4D68-9074-816630C0D282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558CEA10-37D2-4772-B8D9-90FB966EF78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="1005" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listening" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -1101,65 +1101,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="C1">
+        <f>SUM(C3:C102)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <f>A2+1</f>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <f t="shared" ref="A4:A67" si="0">A3+1</f>
-        <v>103</v>
+        <f>A3+1</f>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <f t="shared" si="0"/>
-        <v>104</v>
+        <f t="shared" ref="A5:A68" si="0">A4+1</f>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1168,10 +1162,10 @@
     <row r="6" spans="1:4">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1180,10 +1174,10 @@
     <row r="7" spans="1:4">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1192,10 +1186,10 @@
     <row r="8" spans="1:4">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1204,34 +1198,34 @@
     <row r="9" spans="1:4">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1240,10 +1234,10 @@
     <row r="12" spans="1:4">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1252,10 +1246,10 @@
     <row r="13" spans="1:4">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1264,22 +1258,22 @@
     <row r="14" spans="1:4">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
         <f t="shared" si="0"/>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1288,10 +1282,10 @@
     <row r="16" spans="1:4">
       <c r="A16">
         <f t="shared" si="0"/>
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1300,22 +1294,22 @@
     <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1324,10 +1318,10 @@
     <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1336,22 +1330,22 @@
     <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1360,22 +1354,22 @@
     <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1384,10 +1378,10 @@
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1396,22 +1390,22 @@
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1420,70 +1414,70 @@
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
         <v>6</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1492,10 +1486,10 @@
     <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1504,10 +1498,10 @@
     <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1516,10 +1510,10 @@
     <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1528,10 +1522,10 @@
     <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1540,10 +1534,10 @@
     <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1552,10 +1546,10 @@
     <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1564,10 +1558,10 @@
     <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1576,10 +1570,10 @@
     <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1588,7 +1582,7 @@
     <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
@@ -1600,7 +1594,7 @@
     <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
@@ -1612,10 +1606,10 @@
     <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1624,10 +1618,10 @@
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1636,10 +1630,10 @@
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1648,10 +1642,10 @@
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1660,10 +1654,10 @@
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1672,10 +1666,10 @@
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1684,10 +1678,10 @@
     <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1696,10 +1690,10 @@
     <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1708,10 +1702,10 @@
     <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -1720,10 +1714,10 @@
     <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1732,10 +1726,10 @@
     <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1744,287 +1738,437 @@
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
-        <v>153</v>
+        <v>152</v>
+      </c>
+      <c r="B54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="B57" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
-        <v>157</v>
+        <v>156</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
-        <v>158</v>
+        <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
-        <v>159</v>
+        <v>158</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
-        <v>160</v>
+        <v>159</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
-        <v>162</v>
+        <v>161</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
+        <v>162</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <f t="shared" si="0"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65">
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66">
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67">
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68">
-        <f t="shared" ref="A68:A101" si="1">A67+1</f>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69">
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70">
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71">
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72">
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73">
+      <c r="B73" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74">
+      <c r="B74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75">
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76">
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77">
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78">
+    <row r="79" spans="1:3">
+      <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79">
+    <row r="80" spans="1:3">
+      <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80">
-        <f t="shared" si="1"/>
-        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
         <f t="shared" si="1"/>
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
         <f t="shared" si="1"/>
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
         <f t="shared" si="1"/>
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
         <f t="shared" si="1"/>
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
         <f t="shared" si="1"/>
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
         <f t="shared" si="1"/>
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
         <f t="shared" si="1"/>
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
         <f t="shared" si="1"/>
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
         <f t="shared" si="1"/>
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
         <f t="shared" si="1"/>
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
         <f t="shared" si="1"/>
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
         <f t="shared" si="1"/>
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
         <f t="shared" si="1"/>
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
         <f t="shared" si="1"/>
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
         <f t="shared" si="1"/>
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
         <f t="shared" si="1"/>
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
         <f t="shared" si="1"/>
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
         <f t="shared" si="1"/>
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
+        <f t="shared" si="1"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558CEA10-37D2-4772-B8D9-90FB966EF78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD88E9B-8B89-488C-9A44-358181F30833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="210" windowWidth="13785" windowHeight="15045" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listening" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -95,12 +95,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -115,8 +121,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -397,40 +404,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="C1">
+        <f>SUM(C3:C102)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -438,38 +440,37 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <f>A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <f t="shared" ref="A5:A64" si="0">A4+1</f>
-        <v>4</v>
+        <f>A4+1</f>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="A6:A69" si="0">A5+1</f>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -478,10 +479,10 @@
     <row r="7" spans="1:4">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -490,10 +491,10 @@
     <row r="8" spans="1:4">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -502,52 +503,52 @@
     <row r="9" spans="1:4">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -556,7 +557,7 @@
     <row r="13" spans="1:4">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
@@ -568,34 +569,34 @@
     <row r="14" spans="1:4">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -604,10 +605,10 @@
     <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -616,10 +617,10 @@
     <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -628,10 +629,10 @@
     <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -640,10 +641,10 @@
     <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -652,10 +653,10 @@
     <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -664,10 +665,10 @@
     <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -676,34 +677,34 @@
     <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -712,31 +713,31 @@
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
@@ -748,10 +749,10 @@
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -760,10 +761,10 @@
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -772,10 +773,10 @@
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -784,10 +785,10 @@
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -796,7 +797,7 @@
     <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
@@ -808,10 +809,10 @@
     <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -820,10 +821,10 @@
     <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -832,10 +833,10 @@
     <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -844,22 +845,22 @@
     <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>5</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -868,22 +869,22 @@
     <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -892,31 +893,31 @@
     <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
@@ -928,10 +929,10 @@
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -940,10 +941,10 @@
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -952,7 +953,7 @@
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
@@ -964,10 +965,10 @@
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -976,7 +977,7 @@
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
         <v>6</v>
@@ -988,10 +989,10 @@
     <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1000,10 +1001,10 @@
     <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1012,85 +1013,445 @@
     <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <f t="shared" si="0"/>
         <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1">
+        <f t="shared" ref="A70:A102" si="1">A69+1</f>
+        <v>68</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1107,7 +1468,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2028,110 +2389,170 @@
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
+      <c r="B78" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
+      <c r="B86" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD88E9B-8B89-488C-9A44-358181F30833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEBE535-0891-49C5-99DA-863F19C15D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="210" windowWidth="13785" windowHeight="15045" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13245" yWindow="0" windowWidth="15975" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listening" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -95,7 +95,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,6 +105,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -121,9 +127,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -410,7 +418,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1275,144 +1283,252 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73">
+      <c r="A73" s="2">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
+      <c r="B73" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74">
+      <c r="A74" s="2">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
+      <c r="B74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75">
+      <c r="A75" s="2">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
+      <c r="B75" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76">
+      <c r="A76" s="2">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
+      <c r="B76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77">
+      <c r="A77" s="2">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
+      <c r="B77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78">
+      <c r="A78" s="2">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
+      <c r="B78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79">
+      <c r="A79" s="3">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
+      <c r="B79" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80">
+      <c r="A80" s="3">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81">
+      <c r="B80" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="3">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82">
+      <c r="B81" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="2">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83">
+      <c r="B82" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="2">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84">
+      <c r="B83" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="2">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85">
+      <c r="B84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="2">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86">
+      <c r="B85" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="2">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87">
+      <c r="B86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="2">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88">
+      <c r="B87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="2">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89">
+      <c r="B88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="2">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90">
+      <c r="B89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="2">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-    </row>
-    <row r="91" spans="1:1">
+      <c r="B90" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -1468,7 +1584,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2509,86 +2625,146 @@
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
+      <c r="B91" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
+      <c r="B92" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
+      <c r="B93" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEBE535-0891-49C5-99DA-863F19C15D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F95E1BC-7FE2-48D5-BCFF-1F9B2724E2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13245" yWindow="0" windowWidth="15975" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="listening" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="8">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -95,7 +95,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -111,6 +111,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -130,8 +136,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -418,7 +424,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1283,218 +1289,218 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="2">
+      <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2">
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="2">
+      <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="2">
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="2">
+      <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C75" s="2">
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="2">
+      <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="2">
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="2">
+      <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="2">
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="2">
+      <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="2">
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="3">
+      <c r="A79" s="2">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C79" s="3">
+      <c r="B79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="3">
+      <c r="A80" s="2">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="3">
+      <c r="B80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="3">
+      <c r="A81" s="2">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="3">
+      <c r="B81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="2">
+      <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C82" s="2">
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="2">
+      <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="2">
+      <c r="B83" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="2">
+      <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" s="2">
+      <c r="B84" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="2">
+      <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="2">
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="2">
+      <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="2">
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="2">
+      <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="2">
+      <c r="B87" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="2">
+      <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="2">
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="2">
+      <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="2">
+      <c r="B89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="2">
+      <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C90" s="2">
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90">
         <v>1</v>
       </c>
     </row>
@@ -1503,71 +1509,143 @@
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
+      <c r="B93" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
+      <c r="B95" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100">
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="3">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101">
+      <c r="B100" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="3">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102">
+      <c r="B101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1584,7 +1662,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2745,29 +2823,59 @@
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
+      <c r="B98" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
+      </c>
+      <c r="B102" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/toeic-test-v5/trial_v1.xlsx
+++ b/toeic-test-v5/trial_v1.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F95E1BC-7FE2-48D5-BCFF-1F9B2724E2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BD71B4-35EA-4B07-9BB2-32E99A0103FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="listening" sheetId="1" r:id="rId1"/>
-    <sheet name="reading" sheetId="2" r:id="rId2"/>
+    <sheet name="summary" sheetId="3" r:id="rId1"/>
+    <sheet name="listening" sheetId="1" r:id="rId2"/>
+    <sheet name="reading" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="12">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -72,6 +73,28 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>reading</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>listening</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正解率</t>
+    <rPh sb="0" eb="3">
+      <t>セイカイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題数</t>
+    <rPh sb="0" eb="3">
+      <t>モンダイスウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -133,11 +156,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -417,6 +441,157 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8589702-E812-4623-BA9C-754741ECDB80}">
+  <dimension ref="B2:E11"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <f>SUM(listening!C3:C12)</f>
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4">
+        <f>C3/D3</f>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <f>SUM(listening!C13:C42)</f>
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" ref="E4:E6" si="0">C4/D4</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <f>SUM(listening!C43:C72)</f>
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <f>SUM(listening!C73:C102)</f>
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <f>SUM(reading!C3:C42)</f>
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" ref="E9:E11" si="1">C9/D9</f>
+        <v>0.72499999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <f>SUM(reading!C43:C54)</f>
+        <v>12</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <f>SUM(reading!C55:C102)</f>
+        <v>42</v>
+      </c>
+      <c r="D11">
+        <v>48</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1654,7 +1829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
   <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
